--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/melilith.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/melilith.xlsx
@@ -512,7 +512,7 @@
           <t>You...are you lost? Or did you come here to play?</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Você... está perdido? Ou veio aqui para brincar?</t>
         </is>
@@ -553,9 +553,9 @@
           <t>Oh, what's the matter...#brother2?</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Oh, o que houve...#brother2?</t>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>Oh, que foi...#brother2?</t>
         </is>
       </c>
     </row>
@@ -644,9 +644,9 @@
           <t>You...are you lost? Or did you come here to play?</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você... está perdido? Ou veio aqui para brincar?  </t>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>Você... está perdido? Ou veio aqui para brincar?</t>
         </is>
       </c>
     </row>
@@ -666,11 +666,10 @@
 Not many visitors come here. Some even call this a cursed mansion. Tell me, will you play with me?</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bem-vindo à minha mansão. Pode ser velha e um pouco bagunçada, mas por favor, sinta-se em casa. Meu nome é Melilith. É um nome bem de princesa, não acha?  _x000D_
-_x000D_
-Poucos visitantes vêm aqui. Alguns até chamam este lugar de mansão amaldiçoada. Diga-me, você vai brincar comigo?  </t>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>Bem-vindo à minha mansão. Pode ser velha e um pouco bagunçada, mas fique à vontade. Meu nome é Melilith. É um nome bem de princesa, não é?
+Poucos visitantes vêm aqui. Alguns até chamam isto de mansão amaldiçoada. Diga, vai brincar comigo?</t>
         </is>
       </c>
     </row>
@@ -698,9 +697,9 @@
           <t>Yes.</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sim  </t>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>Sim.</t>
         </is>
       </c>
     </row>
@@ -728,9 +727,9 @@
           <t>No.</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não  </t>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>Não.</t>
         </is>
       </c>
     </row>
@@ -760,9 +759,9 @@
           <t>I see... Yes, it makes sense. Who would want to play in a dark, old mansion...</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Entendo... Sim, faz sentido. Quem iria querer brincar em uma mansão velha e sombria...</t>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>Entendo... Sim, faz sentido. Quem iria querer brincar numa mansão velha e escura...</t>
         </is>
       </c>
     </row>
@@ -794,9 +793,9 @@
           <t xml:space="preserve">Really?...I'm so glad! </t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sério?... Isso me deixa tão feliz!  </t>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">De verdade?...Fico tão contente! </t>
         </is>
       </c>
     </row>
@@ -814,9 +813,9 @@
           <t>The truth is, occasionally playing games with visitors like this is my only joy. What game would you prefer? Hide and seek? Catch and catch? ...Ah, right, since you seem to be an adventurer, let's go on a treasure hunt!</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A verdade é que, de vez em quando, brincar com visitantes assim é minha única alegria. Que jogo você prefere? Esconde-esconde? Pega-pega? ...Ah, certo, já que você parece ser um aventureiro, vamos em uma caça ao tesouro!  </t>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>A verdade é que brincar de jogos com visitantes como este é minha única alegria. Que jogo você prefere? Esconde-esconde? Pega-pega? ...Ah, certo, como você parece ser um aventureiro, vamos caçar um tesouro!</t>
         </is>
       </c>
     </row>
@@ -834,9 +833,9 @@
           <t>A long time ago, I collected lots of treasures deep beneath this mansion. Among these treasures, there's a magical wand that can grant any wish. So, I have a request... Will you go search for the treasure?</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Há muito tempo, eu coletei vários tesouros nas profundezas desta mansão. Entre esses tesouros, há uma varinha mágica que pode conceder qualquer desejo. Então, tenho um pedido... Você vai procurar pelo tesouro?  </t>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>Há muito tempo, colecionei muitos tesouros no fundo desta mansão. Entre esses tesouros, há uma varinha mágica que pode realizar qualquer desejo. Então, tenho um pedido... Você vai procurar o tesouro?</t>
         </is>
       </c>
     </row>
@@ -864,9 +863,9 @@
           <t>Yes.</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sim  </t>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>Sim.</t>
         </is>
       </c>
     </row>
@@ -894,9 +893,9 @@
           <t>No.</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não  </t>
+      <c r="K43" s="8" t="inlineStr">
+        <is>
+          <t>Não.</t>
         </is>
       </c>
     </row>
@@ -921,9 +920,9 @@
           <t>Really?...Oh, how wonderful!</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sério?... Oh, que maravilhoso!  </t>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>De verdade?...Oh, que maravilha!</t>
         </is>
       </c>
     </row>
@@ -944,11 +943,10 @@
 Now, let's get prepared right away. Hehe, it's been centuries since I last had a "treasure hunt". I'm really looking forward to it... I need to invite a lot of friends to welcome you! You're not afraid of undeads, are you?</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você pode ficar com qualquer tesouro que encontrar, mas apenas um. Tenha cuidado! Sempre pegue apenas "um". Se pegar mais do que isso, uma maldição terrível o aguarda.  _x000D_
-_x000D_
-Agora, vamos nos preparar imediatamente. Hehe, faz séculos desde a última vez que participei de uma "caça ao tesouro". Estou realmente ansiosa por isso... Preciso convidar muitos amigos para recebê-lo! Você não tem medo de mortos-vivos, tem?  </t>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>Pode ficar com o tesouro que achar, mas só um. Cuidado! Leve sempre só "um". Mais que isso, uma maldição aterrorizante espera.
+Agora, vamos nos preparar já. Hehe, faz séculos desde minha última "caça ao tesouro". Estou muito animada... Preciso convidar muitos amigos para receber você! Não tem medo de mortos-vivos, tem?</t>
         </is>
       </c>
     </row>
@@ -1002,9 +1000,9 @@
           <t>Well, the game is about to begin... When you're ready, head down the stairs to the basement. Be careful, brave adventurer.</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bem, o jogo está prestes a começar... Quando estiver pronto, desça as escadas até o porão. Tenha cuidado, bravo aventureiro.  </t>
+      <c r="K53" s="8" t="inlineStr">
+        <is>
+          <t>Bom, o jogo está para começar... Quando estiver pronto, desça as escadas até o porão. Cuidado, bravo aventureiro.</t>
         </is>
       </c>
     </row>
@@ -1034,9 +1032,9 @@
           <t>I wonder how the treasure hunt is progressing?... I believe that you will offer us a magnificent scream.</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Como será que a caça ao tesouro está indo?... Acredito que você nos presenteará com um grito magnífico.  </t>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>Será que a caça ao tesouro está progredindo?... Acredito que nos oferecerá um grito magnífico.</t>
         </is>
       </c>
     </row>
@@ -1071,9 +1069,9 @@
           <t>Welcome back. Our fun time has come to an end. Goodbye, brave visitor. I hope you live happily with the treasure you've taken.</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bem-vindo de volta. Nosso momento divertido chegou ao fim. Adeus, bravo visitante. Espero que viva feliz com o tesouro que levou.  </t>
+      <c r="K66" s="8" t="inlineStr">
+        <is>
+          <t>Bem-vindo de volta. Nosso tempo divertido chegou ao fim. Adeus, bravo visitante. Espero que viva feliz com o tesouro que levou.</t>
         </is>
       </c>
     </row>
@@ -1151,9 +1149,9 @@
           <t>...Huh? What is that ragged, dirty scrap of paper?</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...Hã? O que é esse pedaço de papel rasgado e sujo?  </t>
+      <c r="K74" s="8" t="inlineStr">
+        <is>
+          <t>...Hã? Que papel amassado e sujo é esse?</t>
         </is>
       </c>
     </row>
@@ -1171,9 +1169,9 @@
           <t>A ticket to befriend Melilith...No, I made this hundreds of years ago, but no one ever chose it. I had completely forgotten about it. But... did you give up the other treasures for this?</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Um bilhete para se tornar amigo de Melilith... Não, eu fiz isso há centenas de anos, mas ninguém nunca o escolheu. Eu tinha me esquecido completamente disso. Mas... você abriu mão dos outros tesouros por isso?  </t>
+      <c r="K75" s="8" t="inlineStr">
+        <is>
+          <t>Um vale para fazer amizade com Melilith...Não, fiz isto há centenas de anos, mas ninguém nunca o escolheu. Tinha me esquecido completamente. Mas... você desistiu dos outros tesouros por isto?</t>
         </is>
       </c>
     </row>
@@ -1201,9 +1199,9 @@
           <t>Yes.</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sim  </t>
+      <c r="K76" s="8" t="inlineStr">
+        <is>
+          <t>Sim.</t>
         </is>
       </c>
     </row>
@@ -1231,9 +1229,9 @@
           <t>No.</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não  </t>
+      <c r="K77" s="8" t="inlineStr">
+        <is>
+          <t>Não.</t>
         </is>
       </c>
     </row>
@@ -1258,9 +1256,9 @@
           <t>Liar.</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mentiroso.  </t>
+      <c r="K80" s="8" t="inlineStr">
+        <is>
+          <t>Mentiroso.</t>
         </is>
       </c>
     </row>
@@ -1286,9 +1284,9 @@
           <t>I see... That's right. You probably thought there was some value in this scrap of paper, didn't you?... I hope you are cursed.</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Entendo... Isso mesmo. Você provavelmente achou que esse pedaço de papel tinha algum valor, não foi?... Espero que seja amaldiçoado.  </t>
+      <c r="K82" s="8" t="inlineStr">
+        <is>
+          <t>Entendi... É isso. Você provavelmente achou que havia algum valor neste pedaço de papel, não achou?... Espero que seja amaldiçoado.</t>
         </is>
       </c>
     </row>
@@ -1364,9 +1362,9 @@
           <t>...Huh?</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...Hã?  </t>
+      <c r="K90" s="8" t="inlineStr">
+        <is>
+          <t>...Hã?</t>
         </is>
       </c>
     </row>
@@ -1384,9 +1382,9 @@
           <t>You gave up the treasure for such a tattered scrap of paper?</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você desistiu do tesouro por um pedaço de papel tão esfarrapado?  </t>
+      <c r="K91" s="8" t="inlineStr">
+        <is>
+          <t>Você desistiu do tesouro por um pedaço de papel tão esfarrapado?</t>
         </is>
       </c>
     </row>
@@ -1404,9 +1402,9 @@
           <t xml:space="preserve">...The treasure hunt wasn't supposed to be this dangerous at the beginning. I thought someone would soon bring back the ticket and smile at me. </t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...A caça ao tesouro não deveria ser tão perigosa no começo. Achei que alguém logo traria o bilhete de volta e sorriria para mim.  </t>
+      <c r="K92" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">...A caça ao tesouro não era para ser tão perigosa no começo. Achei que alguém logo traria o vale de volta e sorriria para mim. </t>
         </is>
       </c>
     </row>
@@ -1424,9 +1422,9 @@
           <t>But everyone chose other sparkling treasures and left this mansion... so I...</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mas todos escolheram outros tesouros brilhantes e deixaram esta mansão... então eu...  </t>
+      <c r="K93" s="8" t="inlineStr">
+        <is>
+          <t>Mas todos escolheram outros tesouros cintilantes e deixaram esta mansão... então eu...</t>
         </is>
       </c>
     </row>
@@ -1444,9 +1442,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="K94" s="8" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -1464,9 +1462,9 @@
           <t>Tell me, what kind of face should I make at a time like this? I can hardly remember what it was like when I was alive... No, even when I was alive...</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Diga-me, que tipo de expressão eu deveria fazer em um momento como este? Mal consigo me lembrar de como era estar viva... Não, mesmo quando eu estava viva...  </t>
+      <c r="K95" s="8" t="inlineStr">
+        <is>
+          <t>Diga, que cara eu deveria fazer num momento destes? Mal lembro como era quando estava viva... Não, mesmo quando estava viva...</t>
         </is>
       </c>
     </row>
@@ -1484,9 +1482,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="K96" s="8" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -1504,9 +1502,9 @@
           <t>Thank you, my first friend.</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Obrigada, meu primeiro amigo.  </t>
+      <c r="K97" s="8" t="inlineStr">
+        <is>
+          <t>Obrigada, meu primeiro amigo.</t>
         </is>
       </c>
     </row>
